--- a/artfynd/A 35002-2025 artfynd.xlsx
+++ b/artfynd/A 35002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96480998</v>
+        <v>96480988</v>
       </c>
       <c r="B2" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553797.7606463426</v>
+        <v>553720</v>
       </c>
       <c r="R2" t="n">
-        <v>6275824.831906676</v>
+        <v>6275923</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96480988</v>
+        <v>96480992</v>
       </c>
       <c r="B3" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553719.3318860549</v>
+        <v>553742</v>
       </c>
       <c r="R3" t="n">
-        <v>6275922.855825399</v>
+        <v>6275886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +847,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96480992</v>
+        <v>96480998</v>
       </c>
       <c r="B4" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553741.8490800635</v>
+        <v>553798</v>
       </c>
       <c r="R4" t="n">
-        <v>6275886.284020041</v>
+        <v>6275825</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +948,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +981,7 @@
         <v>96481001</v>
       </c>
       <c r="B5" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553800.4335169352</v>
+        <v>553801</v>
       </c>
       <c r="R5" t="n">
-        <v>6275745.093819961</v>
+        <v>6275745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,12 +1082,7 @@
         <v>96481007</v>
       </c>
       <c r="B6" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553803.8461166928</v>
+        <v>553804</v>
       </c>
       <c r="R6" t="n">
-        <v>6275736.88504714</v>
+        <v>6275737</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,19 +1150,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,6 +1177,523 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96481063</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Alsjö 1:27, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>553806</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6275907</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Oskar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96481090</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Alsjö 1:27, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>553821</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6275786</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oskar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96481094</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alsjö 1:27, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>553842</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6275758</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oskar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96480994</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Alsjö 1:29, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>553776</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6275919</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Oskar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sparsam förekomst</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96481060</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Alsjö 1:27, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>553794</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6275915</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Oskar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sparsam förekomst</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35002-2025 artfynd.xlsx
+++ b/artfynd/A 35002-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480988</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480992</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480998</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481007</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481063</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481090</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481094</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96480994</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,8 +1744,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96481060</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>